--- a/data/trans_orig/IP07A04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A04-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse por su aspecto en 2007 (tasa de respuesta: 99,3%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2007 (tasa de respuesta: 99,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16018</t>
+          <t>15428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18737</t>
+          <t>17637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18471</t>
+          <t>18003</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>14118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>15243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28374</t>
+          <t>28830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>11695</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19869</t>
+          <t>20351</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35201</t>
+          <t>34925</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15416</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23432</t>
+          <t>23033</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>15338</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6865</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15782</t>
+          <t>15895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15107</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28586</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26390</t>
+          <t>27405</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44100</t>
+          <t>45134</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18993</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34237</t>
+          <t>34603</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49718</t>
+          <t>50284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72550</t>
+          <t>72702</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42651</t>
+          <t>41683</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62859</t>
+          <t>61553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33731</t>
+          <t>34293</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53146</t>
+          <t>53322</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81040</t>
+          <t>82437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110904</t>
+          <t>110416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55926</t>
+          <t>55826</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77456</t>
+          <t>78579</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52757</t>
+          <t>53598</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74635</t>
+          <t>74953</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>114278</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>144902</t>
+          <t>145566</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,15%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13236</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27331</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35138</t>
+          <t>35165</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53945</t>
+          <t>53811</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51637</t>
+          <t>52179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75242</t>
+          <t>75433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22612</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38997</t>
+          <t>39236</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48714</t>
+          <t>48880</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69641</t>
+          <t>70114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76920</t>
+          <t>77847</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103431</t>
+          <t>102958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23776</t>
+          <t>24214</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16391</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20847</t>
+          <t>21517</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37076</t>
+          <t>37082</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21636</t>
+          <t>21566</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15048</t>
+          <t>14411</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18096</t>
+          <t>18241</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32456</t>
+          <t>32658</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>12056</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23933</t>
+          <t>23807</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20754</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24088</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40812</t>
+          <t>41358</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13901</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17823</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>14697</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28150</t>
+          <t>28124</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13539</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18837</t>
+          <t>18489</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>14817</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28797</t>
+          <t>28308</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50572</t>
+          <t>51842</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74204</t>
+          <t>74318</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30407</t>
+          <t>30021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48628</t>
+          <t>49038</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86384</t>
+          <t>86815</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116815</t>
+          <t>116827</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>66468</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93486</t>
+          <t>92096</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50730</t>
+          <t>50747</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>72556</t>
+          <t>74141</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>123997</t>
+          <t>126304</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>158374</t>
+          <t>159235</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82020</t>
+          <t>81727</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>107992</t>
+          <t>107388</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>81438</t>
+          <t>81067</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>107225</t>
+          <t>107778</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>172884</t>
+          <t>170972</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>210288</t>
+          <t>208064</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>26799</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45152</t>
+          <t>44060</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78504</t>
+          <t>77970</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>86481</t>
+          <t>86857</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>115890</t>
+          <t>116769</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39119</t>
+          <t>39419</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59507</t>
+          <t>61079</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70983</t>
+          <t>70448</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>96422</t>
+          <t>95761</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>116142</t>
+          <t>116446</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>148654</t>
+          <t>148827</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse por su aspecto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14460</t>
+          <t>14714</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27430</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>18742</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>19412</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>16011</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>17222</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30784</t>
+          <t>32422</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16640</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15346</t>
+          <t>15412</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28359</t>
+          <t>29155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14994</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15776</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14367</t>
+          <t>13694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27398</t>
+          <t>26829</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44052</t>
+          <t>44106</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64440</t>
+          <t>66805</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31512</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>51579</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81271</t>
+          <t>80926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109853</t>
+          <t>109023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34426</t>
+          <t>34575</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53760</t>
+          <t>53904</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31522</t>
+          <t>32529</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50917</t>
+          <t>51712</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71268</t>
+          <t>71799</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98403</t>
+          <t>99248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44480</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65039</t>
+          <t>65980</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44974</t>
+          <t>43917</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65445</t>
+          <t>65975</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95504</t>
+          <t>92870</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124167</t>
+          <t>122629</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27375</t>
+          <t>27638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21073</t>
+          <t>21264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37748</t>
+          <t>37921</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59567</t>
+          <t>59166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25235</t>
+          <t>26091</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43239</t>
+          <t>42860</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53280</t>
+          <t>51987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76141</t>
+          <t>75588</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83089</t>
+          <t>84270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>113179</t>
+          <t>112932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17255</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15554</t>
+          <t>15281</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15460</t>
+          <t>15078</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28662</t>
+          <t>29215</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22415</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19312</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34184</t>
+          <t>34605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11548</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>22465</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21830</t>
+          <t>21862</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25386</t>
+          <t>25402</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41956</t>
+          <t>41362</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12179</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13174</t>
+          <t>12827</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>9973</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21844</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18306</t>
+          <t>19224</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8719</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>19321</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19612</t>
+          <t>18704</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34115</t>
+          <t>33755</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66826</t>
+          <t>66054</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92452</t>
+          <t>91765</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46533</t>
+          <t>45506</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68682</t>
+          <t>68107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120395</t>
+          <t>119886</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>155142</t>
+          <t>152392</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54437</t>
+          <t>54333</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>77657</t>
+          <t>79489</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47865</t>
+          <t>47777</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>69842</t>
+          <t>70884</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>105746</t>
+          <t>106867</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>139984</t>
+          <t>139708</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>72429</t>
+          <t>71869</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>97839</t>
+          <t>97399</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>67149</t>
+          <t>68539</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>94246</t>
+          <t>94108</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>146845</t>
+          <t>147013</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>183305</t>
+          <t>182933</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28639</t>
+          <t>28432</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48846</t>
+          <t>47411</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38943</t>
+          <t>38706</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>59590</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70402</t>
+          <t>72512</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99130</t>
+          <t>99753</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45299</t>
+          <t>45333</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67988</t>
+          <t>67829</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>75103</t>
+          <t>74891</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>101677</t>
+          <t>102079</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>127323</t>
+          <t>124729</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>161553</t>
+          <t>160392</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse por su aspecto en 2016 (tasa de respuesta: 98,82%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2016 (tasa de respuesta: 98,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13397</t>
+          <t>13344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9973</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>17801</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10422</t>
+          <t>10062</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19460</t>
+          <t>19423</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13966</t>
+          <t>13378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26172</t>
+          <t>26064</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,08%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>13348</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13040</t>
+          <t>13096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11107</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>23095</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53053</t>
+          <t>54211</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76673</t>
+          <t>76931</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>36236</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55463</t>
+          <t>56802</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96142</t>
+          <t>96404</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126367</t>
+          <t>126283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38786</t>
+          <t>38601</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58349</t>
+          <t>60226</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40137</t>
+          <t>40419</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61509</t>
+          <t>60700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83907</t>
+          <t>84761</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114904</t>
+          <t>114052</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40069</t>
+          <t>39851</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60539</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34628</t>
+          <t>34684</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53994</t>
+          <t>54241</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>78267</t>
+          <t>80086</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109322</t>
+          <t>107792</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27103</t>
+          <t>26284</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45034</t>
+          <t>44323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35497</t>
+          <t>35377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55688</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66629</t>
+          <t>67225</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93274</t>
+          <t>95043</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42017</t>
+          <t>42779</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63338</t>
+          <t>64415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52851</t>
+          <t>51211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75060</t>
+          <t>74006</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99045</t>
+          <t>98776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131071</t>
+          <t>130700</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>21541</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11364</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23644</t>
+          <t>23669</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23119</t>
+          <t>23695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40516</t>
+          <t>40618</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13537</t>
+          <t>13669</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25783</t>
+          <t>25937</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13089</t>
+          <t>13060</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19286</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35837</t>
+          <t>35662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25687</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10897</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22953</t>
+          <t>22510</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25706</t>
+          <t>26751</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>43325</t>
+          <t>44432</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29460</t>
+          <t>29075</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>19522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17321</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31500</t>
+          <t>31540</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28605</t>
+          <t>29341</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>47253</t>
+          <t>47452</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71226</t>
+          <t>70523</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98116</t>
+          <t>97732</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54322</t>
+          <t>53435</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79978</t>
+          <t>79024</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>134098</t>
+          <t>133352</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>170419</t>
+          <t>168585</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61167</t>
+          <t>61310</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>86473</t>
+          <t>86487</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>52083</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76713</t>
+          <t>75911</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>119994</t>
+          <t>120892</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>155770</t>
+          <t>155668</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>63180</t>
+          <t>63387</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>87819</t>
+          <t>88962</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52978</t>
+          <t>51784</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>76352</t>
+          <t>77913</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>120948</t>
+          <t>122928</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>157065</t>
+          <t>157261</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>39071</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58947</t>
+          <t>61045</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59820</t>
+          <t>60032</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85935</t>
+          <t>85814</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>105440</t>
+          <t>104300</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>138798</t>
+          <t>139384</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>62067</t>
+          <t>60844</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>86540</t>
+          <t>85661</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>81576</t>
+          <t>82233</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>109938</t>
+          <t>109746</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>150267</t>
+          <t>150346</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>188656</t>
+          <t>189458</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
